--- a/Logger/Korrelationstabelle_MNW.xlsx
+++ b/Logger/Korrelationstabelle_MNW.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFAA542-5434-422C-9BD4-191EDC2B602A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF6AC29-5188-45A2-8860-681A1F13F556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$126</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="14">
   <si>
     <t>MNW_var</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>MNO</t>
+  </si>
+  <si>
+    <t>MNW</t>
   </si>
   <si>
     <t>MNN</t>
@@ -120,13 +123,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -434,12 +443,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="1" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="15" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -456,7 +465,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -464,10 +473,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0.90353797646594158</v>
+        <v>11</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.99999999999999989</v>
       </c>
     </row>
     <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -475,13 +484,13 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.99365468378650568</v>
+        <v>5</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.85883373444024036</v>
       </c>
     </row>
     <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -489,13 +498,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.98705341618197695</v>
+        <v>5</v>
+      </c>
+      <c r="D4" s="4">
+        <v>-0.63467674415122799</v>
       </c>
     </row>
     <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -503,30 +512,30 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.99222482185477778</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.48943182603179392</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.65352856611836385</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.48999225079161862</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -534,10 +543,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0.89638399142746339</v>
+        <v>13</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.90353797646594158</v>
       </c>
     </row>
     <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -548,10 +557,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0.9926587323139372</v>
+        <v>5</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.99140680147235771</v>
       </c>
     </row>
     <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -559,13 +568,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0.98348237189296628</v>
+        <v>5</v>
+      </c>
+      <c r="D9" s="4">
+        <v>-0.56155257057809504</v>
       </c>
     </row>
     <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -573,41 +582,41 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="2">
-        <v>0.99203392107307009</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D10" s="4">
+        <v>0.71677766117333741</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0.57380020759128891</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.287030906871446</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0.87596249140189753</v>
+        <v>12</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0.89638399142746339</v>
       </c>
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -615,13 +624,13 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="2">
-        <v>0.99140680147235771</v>
+      <c r="D13" s="4">
+        <v>-0.58123989220840766</v>
       </c>
     </row>
     <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -634,7 +643,7 @@
       <c r="C14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="4">
         <v>0.98111050152524981</v>
       </c>
     </row>
@@ -643,41 +652,41 @@
         <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0.98777135518472525</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0.13060061516046659</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="2">
-        <v>0.56642801930014608</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D16" s="4">
+        <v>-0.42040649468751862</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0.86791491458413594</v>
+        <v>11</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0.89199780371558068</v>
       </c>
     </row>
     <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -685,13 +694,13 @@
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="2">
-        <v>0.98600573332281183</v>
+        <v>5</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0.6777880832230091</v>
       </c>
     </row>
     <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -699,13 +708,13 @@
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="2">
-        <v>0.96267073318127006</v>
+        <v>5</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0.1928822325345089</v>
       </c>
     </row>
     <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -716,27 +725,27 @@
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0.98076623035160404</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0.99203392107307009</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0.50310606267959601</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D21" s="4">
+        <v>-3.3785540058600363E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>4</v>
       </c>
@@ -744,10 +753,10 @@
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0.85922983220187987</v>
+        <v>12</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0.87596249140189753</v>
       </c>
     </row>
     <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -755,13 +764,13 @@
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="2">
-        <v>0.96525499786655877</v>
+        <v>5</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0.37596201363018628</v>
       </c>
     </row>
     <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -769,13 +778,13 @@
         <v>7</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" s="2">
-        <v>0.23767270834715909</v>
+        <v>5</v>
+      </c>
+      <c r="D24" s="4">
+        <v>-0.49108941167008258</v>
       </c>
     </row>
     <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -783,41 +792,41 @@
         <v>8</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="2">
-        <v>0.73098660883476463</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D25" s="4">
+        <v>2.646779949243528E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D26" s="2">
-        <v>0.48999225079161862</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D26" s="4">
+        <v>0.56642801930014608</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="2">
-        <v>0.84369873679169283</v>
+        <v>5</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0.86791491458413594</v>
       </c>
     </row>
     <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -830,7 +839,7 @@
       <c r="C28" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="4">
         <v>0.90212992446531171</v>
       </c>
     </row>
@@ -839,13 +848,13 @@
         <v>7</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="2">
-        <v>0.19939966007990781</v>
+      <c r="D29" s="4">
+        <v>-0.62993791679226085</v>
       </c>
     </row>
     <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -853,41 +862,41 @@
         <v>8</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="2">
-        <v>0.71677766117333741</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0.54005323182160359</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="2">
-        <v>0.43615470991361333</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D31" s="4">
+        <v>0.37279546499355182</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="2">
-        <v>0.84331043645896875</v>
+        <v>5</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0.85922983220187987</v>
       </c>
     </row>
     <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -895,13 +904,13 @@
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="2">
-        <v>0.85883373444024036</v>
+        <v>10</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0.98600573332281183</v>
       </c>
     </row>
     <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -909,13 +918,13 @@
         <v>7</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" s="2">
-        <v>0.1928822325345089</v>
+        <v>10</v>
+      </c>
+      <c r="D34" s="4">
+        <v>-0.55788526351411749</v>
       </c>
     </row>
     <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -928,25 +937,25 @@
       <c r="C35" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="4">
         <v>0.71256741700336734</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D36" s="2">
-        <v>0.3990707233061459</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D36" s="4">
+        <v>0.24793004878699529</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>4</v>
       </c>
@@ -954,10 +963,10 @@
         <v>6</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="2">
-        <v>0.83371033733125099</v>
+        <v>13</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0.84369873679169283</v>
       </c>
     </row>
     <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -965,13 +974,13 @@
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" s="2">
-        <v>0.83107639911711106</v>
+        <v>10</v>
+      </c>
+      <c r="D38" s="4">
+        <v>-0.55181614686271496</v>
       </c>
     </row>
     <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -979,13 +988,13 @@
         <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D39" s="2">
-        <v>0.1883249475884505</v>
+        <v>10</v>
+      </c>
+      <c r="D39" s="4">
+        <v>0.96267073318127006</v>
       </c>
     </row>
     <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -993,41 +1002,41 @@
         <v>8</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D40" s="2">
-        <v>0.69260654560272594</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D40" s="4">
+        <v>0.14792873800713219</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="2">
-        <v>0.37279546499355182</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D41" s="4">
+        <v>-0.37845537629574888</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="2">
-        <v>0.60719395389440656</v>
+        <v>10</v>
+      </c>
+      <c r="D42" s="4">
+        <v>0.84331043645896875</v>
       </c>
     </row>
     <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1038,10 +1047,10 @@
         <v>8</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D43" s="2">
-        <v>0.68247951285708564</v>
+        <v>10</v>
+      </c>
+      <c r="D43" s="4">
+        <v>0.66644286066301561</v>
       </c>
     </row>
     <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1049,13 +1058,13 @@
         <v>7</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D44" s="2">
-        <v>-0.40057075464711528</v>
+        <v>10</v>
+      </c>
+      <c r="D44" s="4">
+        <v>0.19939966007990781</v>
       </c>
     </row>
     <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1063,41 +1072,41 @@
         <v>8</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D45" s="2">
-        <v>0.65620513769854105</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D45" s="4">
+        <v>0.98076623035160404</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D46" s="2">
-        <v>0.31351458962509959</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D46" s="4">
+        <v>-5.1355431485196418E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D47" s="2">
-        <v>0.53203670310265361</v>
+        <v>10</v>
+      </c>
+      <c r="D47" s="4">
+        <v>0.83371033733125099</v>
       </c>
     </row>
     <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1105,13 +1114,13 @@
         <v>6</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D48" s="2">
-        <v>0.6777880832230091</v>
+        <v>10</v>
+      </c>
+      <c r="D48" s="4">
+        <v>0.40517559778454959</v>
       </c>
     </row>
     <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1122,10 +1131,10 @@
         <v>9</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D49" s="2">
-        <v>-0.49108941167008258</v>
+        <v>10</v>
+      </c>
+      <c r="D49" s="4">
+        <v>-0.49914265570485777</v>
       </c>
     </row>
     <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1133,30 +1142,30 @@
         <v>8</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D50" s="2">
-        <v>0.54005323182160359</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D50" s="4">
+        <v>4.242530146659778E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51" s="2">
-        <v>0.287030906871446</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D51" s="4">
+        <v>0.43615470991361333</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>4</v>
       </c>
@@ -1164,10 +1173,10 @@
         <v>9</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="2">
-        <v>0.50252356978677659</v>
+        <v>11</v>
+      </c>
+      <c r="D52" s="4">
+        <v>0.66017185485580288</v>
       </c>
     </row>
     <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1175,13 +1184,13 @@
         <v>6</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="2">
-        <v>0.66644286066301561</v>
+        <v>11</v>
+      </c>
+      <c r="D53" s="4">
+        <v>0.89199780371558068</v>
       </c>
     </row>
     <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1189,13 +1198,13 @@
         <v>7</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D54" s="2">
-        <v>-0.49914265570485777</v>
+        <v>11</v>
+      </c>
+      <c r="D54" s="4">
+        <v>-0.63954128600755489</v>
       </c>
     </row>
     <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1206,38 +1215,38 @@
         <v>4</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D55" s="2">
-        <v>0.48943182603179392</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D55" s="4">
+        <v>0.5311690442978606</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D56" s="2">
-        <v>0.25437067304699718</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D56" s="4">
+        <v>0.66017185485580288</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D57" s="2">
-        <v>0.49169466976965892</v>
+        <v>12</v>
+      </c>
+      <c r="D57" s="4">
+        <v>0.60719395389440656</v>
       </c>
     </row>
     <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1245,13 +1254,13 @@
         <v>6</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D58" s="2">
-        <v>0.6434822247688986</v>
+        <v>11</v>
+      </c>
+      <c r="D58" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1259,13 +1268,13 @@
         <v>7</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D59" s="2">
-        <v>-0.53131112015316262</v>
+      <c r="D59" s="4">
+        <v>-0.57774885379150565</v>
       </c>
     </row>
     <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1273,16 +1282,16 @@
         <v>8</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D60" s="2">
-        <v>0.43585425010826062</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D60" s="4">
+        <v>0.71573180947704385</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>9</v>
       </c>
@@ -1290,13 +1299,13 @@
         <v>6</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D61" s="2">
-        <v>0.24793004878699529</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D61" s="4">
+        <v>0.3255175052207025</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>4</v>
       </c>
@@ -1304,10 +1313,10 @@
         <v>9</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D62" s="2">
-        <v>0.49110036012986602</v>
+        <v>5</v>
+      </c>
+      <c r="D62" s="4">
+        <v>0.53203670310265361</v>
       </c>
     </row>
     <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1315,13 +1324,13 @@
         <v>6</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D63" s="2">
-        <v>0.40820817861850422</v>
+      <c r="D63" s="4">
+        <v>-0.57774885379150565</v>
       </c>
     </row>
     <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1329,13 +1338,13 @@
         <v>7</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D64" s="2">
-        <v>-0.54863718405140371</v>
+        <v>11</v>
+      </c>
+      <c r="D64" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1346,27 +1355,27 @@
         <v>7</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D65" s="2">
-        <v>0.15600339871338981</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D65" s="4">
+        <v>0.14823253997567551</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D66" s="2">
-        <v>-2.267804674114381E-2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D66" s="4">
+        <v>-0.44929204457982669</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>4</v>
       </c>
@@ -1374,10 +1383,10 @@
         <v>8</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67" s="2">
-        <v>0.4825951540356615</v>
+        <v>11</v>
+      </c>
+      <c r="D67" s="4">
+        <v>0.5311690442978606</v>
       </c>
     </row>
     <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1385,13 +1394,13 @@
         <v>6</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D68" s="2">
-        <v>0.40517559778454959</v>
+        <v>11</v>
+      </c>
+      <c r="D68" s="4">
+        <v>0.71573180947704385</v>
       </c>
     </row>
     <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1399,13 +1408,13 @@
         <v>7</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D69" s="2">
-        <v>-0.55788526351411749</v>
+        <v>11</v>
+      </c>
+      <c r="D69" s="4">
+        <v>0.14823253997567551</v>
       </c>
     </row>
     <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1413,16 +1422,16 @@
         <v>8</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D70" s="2">
-        <v>0.14792873800713219</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D70" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>9</v>
       </c>
@@ -1430,24 +1439,24 @@
         <v>8</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D71" s="2">
-        <v>-3.3785540058600363E-2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D71" s="4">
+        <v>4.8811232869631254E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D72" s="2">
-        <v>0.4666585528015415</v>
+      <c r="D72" s="4">
+        <v>0.50252356978677659</v>
       </c>
     </row>
     <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1458,10 +1467,10 @@
         <v>9</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D73" s="2">
-        <v>0.37596201363018628</v>
+        <v>11</v>
+      </c>
+      <c r="D73" s="4">
+        <v>0.3255175052207025</v>
       </c>
     </row>
     <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1469,13 +1478,13 @@
         <v>7</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D74" s="2">
-        <v>-0.56155257057809504</v>
+        <v>11</v>
+      </c>
+      <c r="D74" s="4">
+        <v>-0.44929204457982669</v>
       </c>
     </row>
     <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1483,30 +1492,30 @@
         <v>8</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D75" s="2">
-        <v>0.13060061516046659</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D75" s="4">
+        <v>4.8811232869631254E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D76" s="2">
-        <v>-5.1355431485196418E-2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="D76" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>4</v>
       </c>
@@ -1516,8 +1525,8 @@
       <c r="C77" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D77" s="2">
-        <v>0.44433557733115542</v>
+      <c r="D77" s="4">
+        <v>0.49169466976965892</v>
       </c>
     </row>
     <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1525,13 +1534,13 @@
         <v>6</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D78" s="2">
-        <v>0.33775358351924772</v>
+      <c r="D78" s="4">
+        <v>0.83107639911711106</v>
       </c>
     </row>
     <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1539,13 +1548,13 @@
         <v>7</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D79" s="2">
-        <v>-0.59376826142996242</v>
+        <v>12</v>
+      </c>
+      <c r="D79" s="4">
+        <v>-0.66237358922467171</v>
       </c>
     </row>
     <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1553,41 +1562,41 @@
         <v>8</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D80" s="2">
-        <v>0.1100184387547023</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D80" s="4">
+        <v>0.43585425010826062</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D81" s="2">
-        <v>-6.2188005711506372E-2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D81" s="4">
+        <v>0.57380020759128891</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D82" s="2">
-        <v>-0.57336521172137123</v>
+        <v>13</v>
+      </c>
+      <c r="D82" s="4">
+        <v>0.49110036012986602</v>
       </c>
     </row>
     <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1595,13 +1604,13 @@
         <v>6</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D83" s="2">
-        <v>-0.55181614686271496</v>
+        <v>12</v>
+      </c>
+      <c r="D83" s="4">
+        <v>0.99365468378650568</v>
       </c>
     </row>
     <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1609,13 +1618,13 @@
         <v>7</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D84" s="2">
-        <v>-0.59726524729820563</v>
+      <c r="D84" s="4">
+        <v>-0.59376826142996242</v>
       </c>
     </row>
     <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1623,41 +1632,41 @@
         <v>8</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D85" s="2">
-        <v>6.5959644592732722E-2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D85" s="4">
+        <v>0.69260654560272594</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D86" s="2">
-        <v>-0.37845537629574888</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D86" s="4">
+        <v>0.31351458962509959</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D87" s="2">
-        <v>-0.58912112893665303</v>
+        <v>5</v>
+      </c>
+      <c r="D87" s="4">
+        <v>0.4825951540356615</v>
       </c>
     </row>
     <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1670,8 +1679,8 @@
       <c r="C88" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D88" s="2">
-        <v>-0.55877168147948353</v>
+      <c r="D88" s="4">
+        <v>-0.59886048670040559</v>
       </c>
     </row>
     <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1679,13 +1688,13 @@
         <v>7</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D89" s="2">
-        <v>-0.62993791679226085</v>
+        <v>12</v>
+      </c>
+      <c r="D89" s="4">
+        <v>0.98705341618197695</v>
       </c>
     </row>
     <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1693,16 +1702,16 @@
         <v>8</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D90" s="2">
-        <v>4.242530146659778E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D90" s="4">
+        <v>0.1100184387547023</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>9</v>
       </c>
@@ -1712,22 +1721,22 @@
       <c r="C91" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D91" s="2">
-        <v>-0.39332099001717002</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D91" s="4">
+        <v>-0.42810521109428518</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D92" s="2">
-        <v>-0.61956676452778481</v>
+        <v>10</v>
+      </c>
+      <c r="D92" s="4">
+        <v>0.4666585528015415</v>
       </c>
     </row>
     <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1735,13 +1744,13 @@
         <v>6</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D93" s="2">
-        <v>-0.58123989220840766</v>
+        <v>12</v>
+      </c>
+      <c r="D93" s="4">
+        <v>0.68247951285708564</v>
       </c>
     </row>
     <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1749,13 +1758,13 @@
         <v>7</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D94" s="2">
-        <v>-0.63467674415122799</v>
+        <v>12</v>
+      </c>
+      <c r="D94" s="4">
+        <v>0.1883249475884505</v>
       </c>
     </row>
     <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1763,41 +1772,41 @@
         <v>8</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D95" s="2">
-        <v>3.3506251387864901E-2</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D95" s="4">
+        <v>0.99222482185477778</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D96" s="2">
-        <v>-0.42040649468751862</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D96" s="4">
+        <v>-2.267804674114381E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D97" s="2">
-        <v>-0.63932335607235058</v>
+        <v>13</v>
+      </c>
+      <c r="D97" s="4">
+        <v>0.44433557733115542</v>
       </c>
     </row>
     <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1805,13 +1814,13 @@
         <v>6</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D98" s="2">
-        <v>-0.59886048670040559</v>
+        <v>12</v>
+      </c>
+      <c r="D98" s="4">
+        <v>0.40820817861850422</v>
       </c>
     </row>
     <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1819,13 +1828,13 @@
         <v>7</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D99" s="2">
-        <v>-0.66237358922467171</v>
+        <v>12</v>
+      </c>
+      <c r="D99" s="4">
+        <v>-0.53131112015316262</v>
       </c>
     </row>
     <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1836,35 +1845,385 @@
         <v>9</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D100" s="2">
-        <v>2.646779949243528E-2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D100" s="4">
+        <v>3.3506251387864901E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D101" s="2">
-        <v>-0.42810521109428518</v>
+        <v>12</v>
+      </c>
+      <c r="D101" s="4">
+        <v>0.65352856611836385</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" s="4">
+        <v>-0.57336521172137123</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D103" s="4">
+        <v>0.96525499786655877</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D104" s="4">
+        <v>-0.59726524729820563</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" s="4">
+        <v>0.65620513769854105</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" s="4">
+        <v>0.3990707233061459</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D107" s="4">
+        <v>-0.58912112893665303</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D108" s="4">
+        <v>0.9926587323139372</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D109" s="4">
+        <v>-0.54863718405140371</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D110" s="4">
+        <v>0.73098660883476463</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D111" s="4">
+        <v>0.25437067304699718</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D112" s="4">
+        <v>-0.61956676452778481</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D113" s="4">
+        <v>-0.55877168147948353</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D114" s="4">
+        <v>0.98348237189296628</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D115" s="4">
+        <v>0.15600339871338981</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" s="4">
+        <v>-0.39332099001717002</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D117" s="4">
+        <v>-0.63932335607235058</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D118" s="4">
+        <v>0.6434822247688986</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D119" s="4">
+        <v>0.23767270834715909</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D120" s="4">
+        <v>0.98777135518472525</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D121" s="4">
+        <v>-6.2188005711506372E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" s="4">
+        <v>-0.63954128600755489</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D123" s="4">
+        <v>0.33775358351924772</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D124" s="4">
+        <v>-0.40057075464711528</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D125" s="4">
+        <v>6.5959644592732722E-2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D126" s="4">
+        <v>0.50310606267959601</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D101" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:D126" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Licht_lux"/>
+        <filter val="Temp_sonne_C"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D101">
-      <sortCondition descending="1" ref="D1:D101"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D122">
+      <sortCondition descending="1" ref="D1:D126"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Logger/Korrelationstabelle_MNW.xlsx
+++ b/Logger/Korrelationstabelle_MNW.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF6AC29-5188-45A2-8860-681A1F13F556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5790A41B-CAF5-4DFC-BDE7-D289EED54E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -465,7 +465,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -493,18 +493,18 @@
         <v>0.85883373444024036</v>
       </c>
     </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D4" s="4">
-        <v>-0.63467674415122799</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -535,7 +535,7 @@
         <v>0.48999225079161862</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -563,18 +563,18 @@
         <v>0.99140680147235771</v>
       </c>
     </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D9" s="4">
-        <v>-0.56155257057809504</v>
+        <v>0.98705341618197695</v>
       </c>
     </row>
     <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -605,7 +605,7 @@
         <v>0.287030906871446</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
@@ -633,7 +633,7 @@
         <v>-0.58123989220840766</v>
       </c>
     </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
@@ -641,10 +641,10 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D14" s="4">
-        <v>0.98111050152524981</v>
+        <v>0.98348237189296628</v>
       </c>
     </row>
     <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -675,7 +675,7 @@
         <v>-0.42040649468751862</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>4</v>
       </c>
@@ -703,18 +703,18 @@
         <v>0.6777880832230091</v>
       </c>
     </row>
-    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D19" s="4">
-        <v>0.1928822325345089</v>
+        <v>0.98111050152524981</v>
       </c>
     </row>
     <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -745,7 +745,7 @@
         <v>-3.3785540058600363E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>4</v>
       </c>
@@ -773,18 +773,18 @@
         <v>0.37596201363018628</v>
       </c>
     </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D24" s="4">
-        <v>-0.49108941167008258</v>
+        <v>0.96267073318127006</v>
       </c>
     </row>
     <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -815,7 +815,7 @@
         <v>0.56642801930014608</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>4</v>
       </c>
@@ -843,18 +843,18 @@
         <v>0.90212992446531171</v>
       </c>
     </row>
-    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D29" s="4">
-        <v>-0.62993791679226085</v>
+        <v>0.23767270834715909</v>
       </c>
     </row>
     <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -885,7 +885,7 @@
         <v>0.37279546499355182</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>4</v>
       </c>
@@ -913,18 +913,18 @@
         <v>0.98600573332281183</v>
       </c>
     </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="4">
-        <v>-0.55788526351411749</v>
+        <v>0.19939966007990781</v>
       </c>
     </row>
     <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -955,7 +955,7 @@
         <v>0.24793004878699529</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>4</v>
       </c>
@@ -983,18 +983,18 @@
         <v>-0.55181614686271496</v>
       </c>
     </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D39" s="4">
-        <v>0.96267073318127006</v>
+        <v>0.1928822325345089</v>
       </c>
     </row>
     <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1025,7 +1025,7 @@
         <v>-0.37845537629574888</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>4</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>0.66644286066301561</v>
       </c>
     </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
@@ -1061,10 +1061,10 @@
         <v>8</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D44" s="4">
-        <v>0.19939966007990781</v>
+        <v>0.1883249475884505</v>
       </c>
     </row>
     <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1095,7 +1095,7 @@
         <v>-5.1355431485196418E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>4</v>
       </c>
@@ -1123,18 +1123,18 @@
         <v>0.40517559778454959</v>
       </c>
     </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D49" s="4">
-        <v>-0.49914265570485777</v>
+        <v>0.14823253997567551</v>
       </c>
     </row>
     <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1165,7 +1165,7 @@
         <v>0.43615470991361333</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>4</v>
       </c>
@@ -1193,18 +1193,18 @@
         <v>0.89199780371558068</v>
       </c>
     </row>
-    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D54" s="4">
-        <v>-0.63954128600755489</v>
+        <v>-0.40057075464711528</v>
       </c>
     </row>
     <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1235,7 +1235,7 @@
         <v>0.66017185485580288</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>4</v>
       </c>
@@ -1263,18 +1263,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D59" s="4">
-        <v>-0.57774885379150565</v>
+        <v>-0.44929204457982669</v>
       </c>
     </row>
     <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1305,7 +1305,7 @@
         <v>0.3255175052207025</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>4</v>
       </c>
@@ -1333,18 +1333,18 @@
         <v>-0.57774885379150565</v>
       </c>
     </row>
-    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D64" s="4">
-        <v>1</v>
+        <v>-0.49108941167008258</v>
       </c>
     </row>
     <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1375,7 +1375,7 @@
         <v>-0.44929204457982669</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>4</v>
       </c>
@@ -1403,18 +1403,18 @@
         <v>0.71573180947704385</v>
       </c>
     </row>
-    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D69" s="4">
-        <v>0.14823253997567551</v>
+        <v>-0.49914265570485777</v>
       </c>
     </row>
     <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1445,7 +1445,7 @@
         <v>4.8811232869631254E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>4</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>0.3255175052207025</v>
       </c>
     </row>
-    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>7</v>
       </c>
@@ -1481,10 +1481,10 @@
         <v>9</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D74" s="4">
-        <v>-0.44929204457982669</v>
+        <v>-0.53131112015316262</v>
       </c>
     </row>
     <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1515,7 +1515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>4</v>
       </c>
@@ -1543,18 +1543,18 @@
         <v>0.83107639911711106</v>
       </c>
     </row>
-    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D79" s="4">
-        <v>-0.66237358922467171</v>
+        <v>-0.54863718405140371</v>
       </c>
     </row>
     <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1585,7 +1585,7 @@
         <v>0.57380020759128891</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>4</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>0.99365468378650568</v>
       </c>
     </row>
-    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>7</v>
       </c>
@@ -1621,10 +1621,10 @@
         <v>6</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D84" s="4">
-        <v>-0.59376826142996242</v>
+        <v>-0.55788526351411749</v>
       </c>
     </row>
     <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1655,7 +1655,7 @@
         <v>0.31351458962509959</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>4</v>
       </c>
@@ -1683,18 +1683,18 @@
         <v>-0.59886048670040559</v>
       </c>
     </row>
-    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D89" s="4">
-        <v>0.98705341618197695</v>
+        <v>-0.56155257057809504</v>
       </c>
     </row>
     <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1725,7 +1725,7 @@
         <v>-0.42810521109428518</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>4</v>
       </c>
@@ -1753,18 +1753,18 @@
         <v>0.68247951285708564</v>
       </c>
     </row>
-    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D94" s="4">
-        <v>0.1883249475884505</v>
+        <v>-0.57774885379150565</v>
       </c>
     </row>
     <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1795,7 +1795,7 @@
         <v>-2.267804674114381E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>4</v>
       </c>
@@ -1823,18 +1823,18 @@
         <v>0.40820817861850422</v>
       </c>
     </row>
-    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D99" s="4">
-        <v>-0.53131112015316262</v>
+        <v>-0.59376826142996242</v>
       </c>
     </row>
     <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1865,7 +1865,7 @@
         <v>0.65352856611836385</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>4</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>0.96525499786655877</v>
       </c>
     </row>
-    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>7</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>0.3990707233061459</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>4</v>
       </c>
@@ -1963,18 +1963,18 @@
         <v>0.9926587323139372</v>
       </c>
     </row>
-    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D109" s="4">
-        <v>-0.54863718405140371</v>
+        <v>-0.62993791679226085</v>
       </c>
     </row>
     <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -2005,7 +2005,7 @@
         <v>0.25437067304699718</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>4</v>
       </c>
@@ -2033,18 +2033,18 @@
         <v>-0.55877168147948353</v>
       </c>
     </row>
-    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D114" s="4">
-        <v>0.98348237189296628</v>
+        <v>-0.63467674415122799</v>
       </c>
     </row>
     <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -2075,7 +2075,7 @@
         <v>-0.39332099001717002</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>4</v>
       </c>
@@ -2103,18 +2103,18 @@
         <v>0.6434822247688986</v>
       </c>
     </row>
-    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D119" s="4">
-        <v>0.23767270834715909</v>
+        <v>-0.63954128600755489</v>
       </c>
     </row>
     <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -2145,7 +2145,7 @@
         <v>-6.2188005711506372E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>4</v>
       </c>
@@ -2173,18 +2173,18 @@
         <v>0.33775358351924772</v>
       </c>
     </row>
-    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D124" s="4">
-        <v>-0.40057075464711528</v>
+        <v>-0.66237358922467171</v>
       </c>
     </row>
     <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -2219,10 +2219,10 @@
   <autoFilter ref="A1:D126" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Temp_sonne_C"/>
+        <filter val="relLF_percent"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D122">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:D124">
       <sortCondition descending="1" ref="D1:D126"/>
     </sortState>
   </autoFilter>

--- a/Logger/Korrelationstabelle_MNW.xlsx
+++ b/Logger/Korrelationstabelle_MNW.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5790A41B-CAF5-4DFC-BDE7-D289EED54E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED1CAD6-D615-427C-ABE5-F6BA6445BA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -484,16 +484,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D3" s="4">
-        <v>0.85883373444024036</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -512,27 +512,27 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D5" s="4">
-        <v>0.48943182603179392</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D6" s="4">
-        <v>0.48999225079161862</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -557,13 +557,13 @@
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D8" s="4">
-        <v>0.99140680147235771</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.99365468378650568</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -582,27 +582,27 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D10" s="4">
-        <v>0.71677766117333741</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.99222482185477778</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D11" s="4">
-        <v>0.287030906871446</v>
+        <v>0.66017185485580288</v>
       </c>
     </row>
     <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -624,16 +624,16 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D13" s="4">
-        <v>-0.58123989220840766</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.9926587323139372</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
@@ -652,27 +652,27 @@
         <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D15" s="4">
-        <v>0.13060061516046659</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.99203392107307009</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D16" s="4">
-        <v>-0.42040649468751862</v>
+        <v>0.65352856611836385</v>
       </c>
     </row>
     <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -694,16 +694,16 @@
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D18" s="4">
-        <v>0.6777880832230091</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.99140680147235771</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -725,24 +725,24 @@
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D20" s="4">
-        <v>0.99203392107307009</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.98777135518472525</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D21" s="4">
-        <v>-3.3785540058600363E-2</v>
+        <v>0.57380020759128891</v>
       </c>
     </row>
     <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -764,16 +764,16 @@
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D23" s="4">
-        <v>0.37596201363018628</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.98600573332281183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>7</v>
       </c>
@@ -792,16 +792,16 @@
         <v>8</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D25" s="4">
-        <v>2.646779949243528E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.98076623035160404</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>9</v>
       </c>
@@ -837,13 +837,13 @@
         <v>4</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D28" s="4">
-        <v>0.90212992446531171</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.96525499786655877</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>7</v>
       </c>
@@ -862,27 +862,27 @@
         <v>8</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D30" s="4">
-        <v>0.54005323182160359</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.73098660883476463</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D31" s="4">
-        <v>0.37279546499355182</v>
+        <v>0.50310606267959601</v>
       </c>
     </row>
     <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -904,16 +904,16 @@
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D33" s="4">
-        <v>0.98600573332281183</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.90212992446531171</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>7</v>
       </c>
@@ -935,24 +935,24 @@
         <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D35" s="4">
-        <v>0.71256741700336734</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.71677766117333741</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D36" s="4">
-        <v>0.24793004878699529</v>
+        <v>0.48999225079161862</v>
       </c>
     </row>
     <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -974,16 +974,16 @@
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D38" s="4">
-        <v>-0.55181614686271496</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.89199780371558068</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>7</v>
       </c>
@@ -1002,27 +1002,27 @@
         <v>8</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D40" s="4">
-        <v>0.14792873800713219</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.71573180947704385</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D41" s="4">
-        <v>-0.37845537629574888</v>
+        <v>0.43615470991361333</v>
       </c>
     </row>
     <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1044,16 +1044,16 @@
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D43" s="4">
-        <v>0.66644286066301561</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.85883373444024036</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
@@ -1072,27 +1072,27 @@
         <v>8</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D45" s="4">
-        <v>0.98076623035160404</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.71256741700336734</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D46" s="4">
-        <v>-5.1355431485196418E-2</v>
+        <v>0.3990707233061459</v>
       </c>
     </row>
     <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1114,16 +1114,16 @@
         <v>6</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D48" s="4">
-        <v>0.40517559778454959</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.83107639911711106</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>7</v>
       </c>
@@ -1142,27 +1142,27 @@
         <v>8</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D50" s="4">
-        <v>4.242530146659778E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.69260654560272594</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D51" s="4">
-        <v>0.43615470991361333</v>
+        <v>0.37279546499355182</v>
       </c>
     </row>
     <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1184,16 +1184,16 @@
         <v>6</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D53" s="4">
-        <v>0.89199780371558068</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.71573180947704385</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>7</v>
       </c>
@@ -1215,24 +1215,24 @@
         <v>4</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D55" s="4">
-        <v>0.5311690442978606</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.65620513769854105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D56" s="4">
-        <v>0.66017185485580288</v>
+        <v>0.3255175052207025</v>
       </c>
     </row>
     <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1254,16 +1254,16 @@
         <v>6</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D58" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.68247951285708564</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>7</v>
       </c>
@@ -1282,16 +1282,16 @@
         <v>8</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D60" s="4">
-        <v>0.71573180947704385</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.54005323182160359</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>9</v>
       </c>
@@ -1299,10 +1299,10 @@
         <v>6</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D61" s="4">
-        <v>0.3255175052207025</v>
+        <v>0.31351458962509959</v>
       </c>
     </row>
     <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1324,16 +1324,16 @@
         <v>6</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D63" s="4">
-        <v>-0.57774885379150565</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.6777880832230091</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>7</v>
       </c>
@@ -1352,27 +1352,27 @@
         <v>8</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D65" s="4">
-        <v>0.14823253997567551</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.5311690442978606</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D66" s="4">
-        <v>-0.44929204457982669</v>
+        <v>0.287030906871446</v>
       </c>
     </row>
     <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1397,13 +1397,13 @@
         <v>8</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D68" s="4">
-        <v>0.71573180947704385</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.66644286066301561</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>7</v>
       </c>
@@ -1422,27 +1422,27 @@
         <v>8</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D70" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.48943182603179392</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D71" s="4">
-        <v>4.8811232869631254E-3</v>
+        <v>0.25437067304699718</v>
       </c>
     </row>
     <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1464,16 +1464,16 @@
         <v>6</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D73" s="4">
-        <v>0.3255175052207025</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.6434822247688986</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>7</v>
       </c>
@@ -1492,27 +1492,27 @@
         <v>8</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D75" s="4">
-        <v>4.8811232869631254E-3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.43585425010826062</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D76" s="4">
-        <v>1</v>
+        <v>0.24793004878699529</v>
       </c>
     </row>
     <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1534,16 +1534,16 @@
         <v>6</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D78" s="4">
-        <v>0.83107639911711106</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.40820817861850422</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>7</v>
       </c>
@@ -1562,27 +1562,27 @@
         <v>8</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D80" s="4">
-        <v>0.43585425010826062</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.15600339871338981</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D81" s="4">
-        <v>0.57380020759128891</v>
+        <v>4.8811232869631254E-3</v>
       </c>
     </row>
     <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1604,16 +1604,16 @@
         <v>6</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D83" s="4">
-        <v>0.99365468378650568</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.40517559778454959</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>7</v>
       </c>
@@ -1632,27 +1632,27 @@
         <v>8</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D85" s="4">
-        <v>0.69260654560272594</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.14823253997567551</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D86" s="4">
-        <v>0.31351458962509959</v>
+        <v>-2.267804674114381E-2</v>
       </c>
     </row>
     <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1674,16 +1674,16 @@
         <v>6</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D88" s="4">
-        <v>-0.59886048670040559</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.37596201363018628</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>7</v>
       </c>
@@ -1705,24 +1705,24 @@
         <v>7</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D90" s="4">
-        <v>0.1100184387547023</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.14792873800713219</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D91" s="4">
-        <v>-0.42810521109428518</v>
+        <v>-3.3785540058600363E-2</v>
       </c>
     </row>
     <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1744,16 +1744,16 @@
         <v>6</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D93" s="4">
-        <v>0.68247951285708564</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.33775358351924772</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>7</v>
       </c>
@@ -1772,16 +1772,16 @@
         <v>8</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D95" s="4">
-        <v>0.99222482185477778</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.13060061516046659</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>9</v>
       </c>
@@ -1789,10 +1789,10 @@
         <v>8</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D96" s="4">
-        <v>-2.267804674114381E-2</v>
+        <v>-5.1355431485196418E-2</v>
       </c>
     </row>
     <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1817,13 +1817,13 @@
         <v>9</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D98" s="4">
-        <v>0.40820817861850422</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.3255175052207025</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>7</v>
       </c>
@@ -1842,27 +1842,27 @@
         <v>8</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D100" s="4">
-        <v>3.3506251387864901E-2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>0.1100184387547023</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D101" s="4">
-        <v>0.65352856611836385</v>
+        <v>-6.2188005711506372E-2</v>
       </c>
     </row>
     <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1884,16 +1884,16 @@
         <v>6</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D103" s="4">
-        <v>0.96525499786655877</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.55181614686271496</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>7</v>
       </c>
@@ -1912,27 +1912,27 @@
         <v>8</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D105" s="4">
-        <v>0.65620513769854105</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>6.5959644592732722E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D106" s="4">
-        <v>0.3990707233061459</v>
+        <v>-0.37845537629574888</v>
       </c>
     </row>
     <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -1954,16 +1954,16 @@
         <v>6</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D108" s="4">
-        <v>0.9926587323139372</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.55877168147948353</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>7</v>
       </c>
@@ -1982,27 +1982,27 @@
         <v>8</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D110" s="4">
-        <v>0.73098660883476463</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4.242530146659778E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D111" s="4">
-        <v>0.25437067304699718</v>
+        <v>-0.39332099001717002</v>
       </c>
     </row>
     <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -2027,13 +2027,13 @@
         <v>7</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D113" s="4">
-        <v>-0.55877168147948353</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.57774885379150565</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>7</v>
       </c>
@@ -2052,16 +2052,16 @@
         <v>8</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D115" s="4">
-        <v>0.15600339871338981</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>3.3506251387864901E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>9</v>
       </c>
@@ -2069,10 +2069,10 @@
         <v>7</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D116" s="4">
-        <v>-0.39332099001717002</v>
+        <v>-0.42040649468751862</v>
       </c>
     </row>
     <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -2094,16 +2094,16 @@
         <v>6</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D118" s="4">
-        <v>0.6434822247688986</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.58123989220840766</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>7</v>
       </c>
@@ -2122,27 +2122,27 @@
         <v>8</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D120" s="4">
-        <v>0.98777135518472525</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>2.646779949243528E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D121" s="4">
-        <v>-6.2188005711506372E-2</v>
+        <v>-0.42810521109428518</v>
       </c>
     </row>
     <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
@@ -2164,16 +2164,16 @@
         <v>6</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D123" s="4">
-        <v>0.33775358351924772</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.59886048670040559</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>7</v>
       </c>
@@ -2195,34 +2195,34 @@
         <v>9</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D125" s="4">
-        <v>6.5959644592732722E-2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>4.8811232869631254E-3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D126" s="4">
-        <v>0.50310606267959601</v>
+        <v>-0.44929204457982669</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D126" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="relLF_percent"/>
+        <filter val="Licht_lux"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:D124">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D126">
       <sortCondition descending="1" ref="D1:D126"/>
     </sortState>
   </autoFilter>
